--- a/pageobjects/testData/files/usersCredentials.xlsx
+++ b/pageobjects/testData/files/usersCredentials.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>admin</t>
   </si>
@@ -98,9 +98,6 @@
     <t>managingProviderForStatusCheck</t>
   </si>
   <si>
-    <t>managingauto@yopmail.com</t>
-  </si>
-  <si>
     <t>otherProviderForStatusCheck</t>
   </si>
   <si>
@@ -110,13 +107,13 @@
     <t>providerLoginCrendentails</t>
   </si>
   <si>
-    <t>testprovider2may@yopmail.com</t>
-  </si>
-  <si>
     <t>otherProviderForProviderStatusCheck</t>
   </si>
   <si>
     <t>testautootherproviderFP@yopmail.com</t>
+  </si>
+  <si>
+    <t>managingautoprovider@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -640,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -648,10 +645,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -659,10 +656,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -670,10 +667,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>

--- a/pageobjects/testData/files/usersCredentials.xlsx
+++ b/pageobjects/testData/files/usersCredentials.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB7A1BD-3D99-4F10-B2F1-F4E4BCB97DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="17280" windowHeight="8880"/>
+    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="userCredentials" sheetId="7" r:id="rId1"/>
@@ -18,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>admin</t>
   </si>
@@ -98,9 +99,6 @@
     <t>managingProviderForStatusCheck</t>
   </si>
   <si>
-    <t>managingauto@yopmail.com</t>
-  </si>
-  <si>
     <t>otherProviderForStatusCheck</t>
   </si>
   <si>
@@ -110,20 +108,20 @@
     <t>providerLoginCrendentails</t>
   </si>
   <si>
-    <t>testprovider2may@yopmail.com</t>
-  </si>
-  <si>
     <t>otherProviderForProviderStatusCheck</t>
   </si>
   <si>
     <t>testautootherproviderFP@yopmail.com</t>
+  </si>
+  <si>
+    <t>managingautoprovider@yopmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -508,18 +506,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.140625" customWidth="1"/>
-    <col min="2" max="2" width="78.5703125" customWidth="1"/>
-    <col min="3" max="3" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.109375" customWidth="1"/>
+    <col min="2" max="2" width="78.5546875" customWidth="1"/>
+    <col min="3" max="3" width="37.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -536,7 +534,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -547,7 +545,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -558,7 +556,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -569,7 +567,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -580,7 +578,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -591,7 +589,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -602,7 +600,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -613,7 +611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -624,7 +622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -635,45 +633,45 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>28</v>
       </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
+      <c r="B13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>29</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -686,9 +684,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pageobjects/testData/files/usersCredentials.xlsx
+++ b/pageobjects/testData/files/usersCredentials.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB7A1BD-3D99-4F10-B2F1-F4E4BCB97DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="17280" windowHeight="8880"/>
   </bookViews>
   <sheets>
     <sheet name="userCredentials" sheetId="7" r:id="rId1"/>
@@ -120,8 +119,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -506,18 +505,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.109375" customWidth="1"/>
-    <col min="2" max="2" width="78.5546875" customWidth="1"/>
-    <col min="3" max="3" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" customWidth="1"/>
+    <col min="2" max="2" width="78.5703125" customWidth="1"/>
+    <col min="3" max="3" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -534,7 +533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -545,7 +544,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -556,7 +555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -567,7 +566,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -578,7 +577,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -589,7 +588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -600,7 +599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -611,7 +610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -622,7 +621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -633,7 +632,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -644,7 +643,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -655,7 +654,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -666,7 +665,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -684,9 +683,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pageobjects/testData/files/usersCredentials.xlsx
+++ b/pageobjects/testData/files/usersCredentials.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
   <si>
     <t>admin</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Qwerty@123</t>
   </si>
   <si>
-    <t>testmymanagingprovider7jan@yopmail.com</t>
-  </si>
-  <si>
     <t>FHDAMobileLogin</t>
   </si>
   <si>
@@ -83,9 +80,6 @@
     <t>downloadFHDCLink</t>
   </si>
   <si>
-    <t>https://drive.usercontent.google.com/download?id=1xiCj98fk3Wpz1D0lxVEP4zE7y-BqsnhU&amp;export=download&amp;authuser=0</t>
-  </si>
-  <si>
     <t>https://drive.usercontent.google.com/download?id=12o8ji31FYZE11zBMFRdDBaHaOYlm1l-1&amp;export=download&amp;authuser=0</t>
   </si>
   <si>
@@ -114,6 +108,9 @@
   </si>
   <si>
     <t>managingautoprovider@yopmail.com</t>
+  </si>
+  <si>
+    <t>https://drive.usercontent.google.com/download?id=1X67Iux833kGxdHmhC0cK6V_NdycIagtx&amp;export=download&amp;authuser=0</t>
   </si>
 </sst>
 </file>
@@ -568,10 +565,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -579,10 +576,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -590,10 +587,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -601,10 +598,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -612,10 +609,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -623,10 +620,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -634,10 +631,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -645,10 +642,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -656,10 +653,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -667,10 +664,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>

--- a/pageobjects/testData/files/usersCredentials.xlsx
+++ b/pageobjects/testData/files/usersCredentials.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBB23D3-E31C-434C-ABB8-9A920B3C5C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="17280" windowHeight="8880"/>
+    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="userCredentials" sheetId="7" r:id="rId1"/>
@@ -18,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
   <si>
     <t>admin</t>
   </si>
@@ -111,13 +112,19 @@
   </si>
   <si>
     <t>https://drive.usercontent.google.com/download?id=1X67Iux833kGxdHmhC0cK6V_NdycIagtx&amp;export=download&amp;authuser=0</t>
+  </si>
+  <si>
+    <t>supreadminautotest@yopmail.com</t>
+  </si>
+  <si>
+    <t>checkuser</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,10 +167,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,18 +508,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" customWidth="1"/>
-    <col min="2" max="2" width="78.5703125" customWidth="1"/>
-    <col min="3" max="3" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.88671875" customWidth="1"/>
+    <col min="2" max="2" width="78.5546875" customWidth="1"/>
+    <col min="3" max="3" width="37.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -530,7 +536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -541,7 +547,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -552,7 +558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -563,7 +569,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -574,7 +580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -585,7 +591,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -596,7 +602,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -607,7 +613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -618,7 +624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -629,18 +635,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -651,18 +657,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -670,6 +676,17 @@
         <v>28</v>
       </c>
       <c r="C14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
         <v>12</v>
       </c>
     </row>
@@ -680,9 +697,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pageobjects/testData/files/usersCredentials.xlsx
+++ b/pageobjects/testData/files/usersCredentials.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBB23D3-E31C-434C-ABB8-9A920B3C5C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="17280" windowHeight="8625"/>
   </bookViews>
   <sheets>
     <sheet name="userCredentials" sheetId="7" r:id="rId1"/>
@@ -72,9 +71,6 @@
     <t>FHDCMobileLogin</t>
   </si>
   <si>
-    <t>testcaregiver2may@yopmail.com</t>
-  </si>
-  <si>
     <t>downloadFHDALink</t>
   </si>
   <si>
@@ -118,13 +114,16 @@
   </si>
   <si>
     <t>checkuser</t>
+  </si>
+  <si>
+    <t>caregiverautotest@yopmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -508,18 +507,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.88671875" customWidth="1"/>
-    <col min="2" max="2" width="78.5546875" customWidth="1"/>
-    <col min="3" max="3" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" customWidth="1"/>
+    <col min="2" max="2" width="78.5703125" customWidth="1"/>
+    <col min="3" max="3" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -536,7 +535,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -547,7 +546,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -558,7 +557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -569,18 +568,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -591,100 +590,100 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>16</v>
       </c>
       <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>24</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -697,9 +696,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pageobjects/testData/files/usersCredentials.xlsx
+++ b/pageobjects/testData/files/usersCredentials.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBB23D3-E31C-434C-ABB8-9A920B3C5C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9492A5A3-1F29-403D-AA93-5968BAE975D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,9 +105,6 @@
     <t>otherProviderForProviderStatusCheck</t>
   </si>
   <si>
-    <t>testautootherproviderFP@yopmail.com</t>
-  </si>
-  <si>
     <t>managingautoprovider@yopmail.com</t>
   </si>
   <si>
@@ -118,6 +115,9 @@
   </si>
   <si>
     <t>checkuser</t>
+  </si>
+  <si>
+    <t>otherautoproviderProv@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -167,9 +167,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -574,7 +575,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -618,7 +619,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -640,7 +641,7 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -650,7 +651,7 @@
       <c r="A12" t="s">
         <v>24</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
@@ -662,7 +663,7 @@
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -672,8 +673,8 @@
       <c r="A14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" t="s">
-        <v>28</v>
+      <c r="B14" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -681,10 +682,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>

--- a/pageobjects/testData/files/usersCredentials.xlsx
+++ b/pageobjects/testData/files/usersCredentials.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9492A5A3-1F29-403D-AA93-5968BAE975D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="17280" windowHeight="8625"/>
   </bookViews>
   <sheets>
     <sheet name="userCredentials" sheetId="7" r:id="rId1"/>
@@ -72,9 +71,6 @@
     <t>FHDCMobileLogin</t>
   </si>
   <si>
-    <t>testcaregiver2may@yopmail.com</t>
-  </si>
-  <si>
     <t>downloadFHDALink</t>
   </si>
   <si>
@@ -118,13 +114,16 @@
   </si>
   <si>
     <t>otherautoproviderProv@yopmail.com</t>
+  </si>
+  <si>
+    <t>caregiverautotest@yopmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -509,18 +508,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.88671875" customWidth="1"/>
-    <col min="2" max="2" width="78.5546875" customWidth="1"/>
-    <col min="3" max="3" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" customWidth="1"/>
+    <col min="2" max="2" width="78.5703125" customWidth="1"/>
+    <col min="3" max="3" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -537,7 +536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -548,7 +547,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -559,7 +558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -570,18 +569,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -592,100 +591,100 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>16</v>
       </c>
       <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>27</v>
-      </c>
       <c r="B14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -698,9 +697,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pageobjects/testData/files/usersCredentials.xlsx
+++ b/pageobjects/testData/files/usersCredentials.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9492A5A3-1F29-403D-AA93-5968BAE975D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECA594B-D2DF-4E04-AA63-FD187FBB8C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="1524" windowWidth="17280" windowHeight="8628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="userCredentials" sheetId="7" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
   <si>
     <t>admin</t>
   </si>
@@ -72,9 +72,6 @@
     <t>FHDCMobileLogin</t>
   </si>
   <si>
-    <t>testcaregiver2may@yopmail.com</t>
-  </si>
-  <si>
     <t>downloadFHDALink</t>
   </si>
   <si>
@@ -118,6 +115,12 @@
   </si>
   <si>
     <t>otherautoproviderProv@yopmail.com</t>
+  </si>
+  <si>
+    <t>caregiverautotest@yopmail.com</t>
+  </si>
+  <si>
+    <t>Kuerty@123</t>
   </si>
 </sst>
 </file>
@@ -566,8 +569,8 @@
       <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -575,10 +578,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -588,8 +591,8 @@
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
+      <c r="C6" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -597,18 +600,18 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -616,10 +619,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -627,68 +630,68 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
+        <v>27</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
+      <c r="C12" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
+        <v>27</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/pageobjects/testData/files/usersCredentials.xlsx
+++ b/pageobjects/testData/files/usersCredentials.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECA594B-D2DF-4E04-AA63-FD187FBB8C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD68B37-BAFE-4719-A63F-407EDA678F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="1524" windowWidth="17280" windowHeight="8628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,10 +170,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -569,7 +568,7 @@
       <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>33</v>
       </c>
     </row>
@@ -580,7 +579,7 @@
       <c r="B5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -591,7 +590,7 @@
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>33</v>
       </c>
     </row>
@@ -602,8 +601,8 @@
       <c r="B7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>33</v>
+      <c r="C7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -635,7 +634,7 @@
       <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>33</v>
       </c>
     </row>
@@ -646,7 +645,7 @@
       <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>33</v>
       </c>
     </row>
@@ -657,7 +656,7 @@
       <c r="B12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>33</v>
       </c>
     </row>
@@ -668,7 +667,7 @@
       <c r="B13" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>33</v>
       </c>
     </row>
@@ -679,7 +678,7 @@
       <c r="B14" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>33</v>
       </c>
     </row>
@@ -690,7 +689,7 @@
       <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>33</v>
       </c>
     </row>

--- a/pageobjects/testData/files/usersCredentials.xlsx
+++ b/pageobjects/testData/files/usersCredentials.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECA594B-D2DF-4E04-AA63-FD187FBB8C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="1524" windowWidth="17280" windowHeight="8628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="1530" windowWidth="17280" windowHeight="8625"/>
   </bookViews>
   <sheets>
     <sheet name="userCredentials" sheetId="7" r:id="rId1"/>
@@ -126,8 +125,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,18 +511,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.88671875" customWidth="1"/>
-    <col min="2" max="2" width="78.5546875" customWidth="1"/>
-    <col min="3" max="3" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" customWidth="1"/>
+    <col min="2" max="2" width="78.5703125" customWidth="1"/>
+    <col min="3" max="3" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -540,7 +539,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -551,7 +550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -562,7 +561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -573,7 +572,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -584,7 +583,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -595,18 +594,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>16</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -617,7 +616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -628,7 +627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -639,7 +638,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -650,7 +649,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -661,7 +660,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -672,7 +671,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -683,7 +682,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -701,9 +700,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
